--- a/docs/LIMS_공정별_열매칭표.xlsx
+++ b/docs/LIMS_공정별_열매칭표.xlsx
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>자동계산 9 · 미저장 14</t>
+          <t>자동계산 9 · 미저장 6</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -540,20 +540,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>현재 QMS 표 없음(인수검사)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
+          <t>📦 인수검사 화면(별도 관리)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>메타+성분 39열</t>
+        </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>열 39개</t>
+          <t>합부·거래처·성분 저장</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>✅ 반영</t>
         </is>
       </c>
     </row>
@@ -565,20 +567,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>현재 QMS 표 없음(인수검사)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
+          <t>📦 인수검사 화면(별도 관리)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>메타+성분 26열</t>
+        </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>열 26개</t>
+          <t>합부·거래처·성분 저장</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>✅ 반영</t>
         </is>
       </c>
     </row>
@@ -615,20 +619,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>현재 QMS 표 없음(인수검사)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
+          <t>📦 인수검사 화면(별도 관리)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>메타+성분 21열</t>
+        </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>열 21개</t>
+          <t>합부·거래처·성분 저장</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>✅ 반영</t>
         </is>
       </c>
     </row>
@@ -694,11 +700,11 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>자동계산 7 · 미저장 13</t>
+          <t>자동계산 7 · 미저장 4</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -719,11 +725,11 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>자동계산 7 · 미저장 12</t>
+          <t>자동계산 7 · 미저장 3</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -793,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -881,12 +887,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>시멘트 MgO</t>
+          <t>cem_sio2</t>
         </is>
       </c>
     </row>
@@ -903,12 +909,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SO3(XRF)</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>시멘트 SO3</t>
+          <t>cem_al2o3</t>
         </is>
       </c>
     </row>
@@ -925,12 +931,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45㎛</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>시멘트 45㎛</t>
+          <t>cem_fe2o3</t>
         </is>
       </c>
     </row>
@@ -947,12 +953,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>시멘트 Blaine</t>
+          <t>cem_cao</t>
         </is>
       </c>
     </row>
@@ -969,188 +975,188 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>원료온도</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>시멘트 밀온도</t>
+          <t>시멘트 MgO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>시멘트공정(밀 출구)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>SO3(XRF)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>시멘트 SO3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>시멘트공정(밀 출구)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>압축강도1일(MPa)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>압축강도 1일</t>
+          <t>cem_na2o</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>시멘트공정(밀 출구)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>압축강도3일(MPa)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>압축강도 3일</t>
+          <t>cem_k2o</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>시멘트공정(밀 출구)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>압축강도7일(MPa)</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>압축강도 7일</t>
+          <t>cem_cl</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>시멘트공정(밀 출구)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>압축강도28일(MPa)</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>압축강도 28일</t>
+          <t>cem_fcao</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>시멘트공정(밀 출구)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>45㎛</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>시멘트 45㎛</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>시멘트공정(밀 출구)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>시멘트 Blaine</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>시멘트공정(밀 출구)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>초결시간(분)</t>
+          <t>원료온도</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>초결시간</t>
+          <t>시멘트 밀온도</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1173,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>종결시간(HH:MM)</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>종결시간</t>
+          <t>품명(품종)</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1195,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>압축강도1일(MPa)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>압축강도 1일</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1217,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>압축강도1일(MPa)</t>
+          <t>압축강도3일(MPa)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>압축강도 1일</t>
+          <t>압축강도 3일</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1239,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>압축강도3일(MPa)</t>
+          <t>압축강도7일(MPa)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>압축강도 3일</t>
+          <t>압축강도 7일</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1261,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>압축강도7일(MPa)</t>
+          <t>압축강도28일(MPa)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>압축강도 7일</t>
+          <t>압축강도 28일</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1283,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>압축강도28일(MPa)</t>
+          <t>6가크롬</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>압축강도 28일</t>
+          <t>6가크롬</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1305,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>Autoclave</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>Autoclave</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1327,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>초결시간(분)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>초결시간</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1349,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>초결시간(분)</t>
+          <t>종결시간(HH:MM)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>초결시간</t>
+          <t>종결시간</t>
         </is>
       </c>
     </row>
@@ -1365,188 +1371,188 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>종결시간(HH:MM)</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>종결시간</t>
+          <t>품명(품종)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>물성 + 출하시멘트</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>압축강도1일(MPa)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>압축강도 1일</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>물성 + 출하시멘트</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>압축강도3일(MPa)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>클링커 SiO2</t>
+          <t>압축강도 3일</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>물성 + 출하시멘트</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>압축강도7일(MPa)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>클링커 Al2O3</t>
+          <t>압축강도 7일</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>물성 + 출하시멘트</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>압축강도28일(MPa)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>클링커 Fe2O3</t>
+          <t>압축강도 28일</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>물성 + 출하시멘트</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>6가크롬</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>클링커 CaO</t>
+          <t>6가크롬</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>물성 + 출하시멘트</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>Autoclave</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>클링커 MgO</t>
+          <t>Autoclave</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>물성 + 출하시멘트</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>초결시간(분)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>클링커 SO3</t>
+          <t>초결시간</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>물성 + 출하시멘트</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>종결시간(HH:MM)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>클링커 Na2O</t>
+          <t>종결시간</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1569,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>클링커 K2O</t>
+          <t>품명(품종)</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1591,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>클링커 SiO2</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1613,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(습식)</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>클링커 Al2O3</t>
         </is>
       </c>
     </row>
@@ -1629,188 +1635,188 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>용중</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>클링커 용적비중(용중)</t>
+          <t>클링커 Fe2O3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>클링커 CaO</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>생료 LOI</t>
+          <t>클링커 MgO</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>SO3</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>생료 SiO2</t>
+          <t>클링커 SO3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>생료 Al2O3</t>
+          <t>클링커 Na2O</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>생료 Fe2O3</t>
+          <t>클링커 K2O</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>생료 CaO</t>
+          <t>클링커 유리석회(f-CaO)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>F-CaO(습식)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>생료 MgO</t>
+          <t>클링커 유리석회(f-CaO)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>용중</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>생료 SO3</t>
+          <t>클링커 용적비중(용중)</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1833,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>생료 Na2O</t>
+          <t>품명(품종)</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1855,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>생료 K2O</t>
+          <t>생료 LOI</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1877,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>생료 SiO2</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1899,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>생료 LOI</t>
+          <t>생료 Al2O3</t>
         </is>
       </c>
     </row>
@@ -1915,12 +1921,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>생료 SiO2</t>
+          <t>생료 Fe2O3</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1943,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>생료 Al2O3</t>
+          <t>생료 CaO</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1965,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>생료 Fe2O3</t>
+          <t>생료 MgO</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1987,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>SO3</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>생료 CaO</t>
+          <t>생료 SO3</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2009,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>생료 MgO</t>
+          <t>생료 Na2O</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2031,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>생료 SO3</t>
+          <t>생료 K2O</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2053,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>석회석(%)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>생료 Na2O</t>
+          <t>rm_mx_lime</t>
         </is>
       </c>
     </row>
@@ -2069,450 +2075,1022 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>Shale(%)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>생료 K2O</t>
+          <t>rm_mx_shale</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>실리카(%)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>rm_mx_silica2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>고품위삼고(%)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>클링커 SiO2</t>
+          <t>rm_mx_sago</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>규석(%)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>클링커 Al2O3</t>
+          <t>rm_mx_silica</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>주물사(%)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>클링커 Fe2O3</t>
+          <t>rm_mx_sand</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>철질(%)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>클링커 CaO</t>
+          <t>rm_mx_iron</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>Coal Shale(%)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>클링커 MgO</t>
+          <t>rm_mx_ash</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>투입량 계(%)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>클링커 SO3</t>
+          <t>rm_mx_total</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>클링커 Na2O</t>
+          <t>품명(품종)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>클링커 K2O</t>
+          <t>생료 LOI</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>생료 SiO2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(습식)</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>생료 Al2O3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>용중</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>클링커 용적비중(용중)</t>
+          <t>생료 Fe2O3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>생료 CaO</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>압축강도1일(MPa)</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>압축강도 1일</t>
+          <t>생료 MgO</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>압축강도3일(MPa)</t>
+          <t>SO3</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>압축강도 3일</t>
+          <t>생료 SO3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>압축강도7일(MPa)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>압축강도 7일</t>
+          <t>생료 Na2O</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>압축강도28일(MPa)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>압축강도 28일</t>
+          <t>생료 K2O</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>석회석(%)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>rm_mx_lime</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>생료</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>초결시간(분)</t>
+          <t>경석(%)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>초결시간</t>
+          <t>rm_mx_shale</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>조합원료성적(생료·킬른 피드)</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>생료</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>규석(%)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>rm_mx_silica</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>조합원료성적(생료·킬른 피드)</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>생료</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>석탄회(%)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>rm_mx_ash</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>조합원료성적(생료·킬른 피드)</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>생료</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>삼고(%)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>rm_mx_sago</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>조합원료성적(생료·킬른 피드)</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>생료</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>철질(%)</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>rm_mx_iron</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>조합원료성적(생료·킬른 피드)</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>생료</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>주물사(%)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>rm_mx_sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>조합원료성적(생료·킬른 피드)</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>생료</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>실리카(%)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>rm_mx_silica2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>조합원료성적(생료·킬른 피드)</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>생료</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>투입량 계(%)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>rm_mx_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>품명</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>품명(품종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>클링커 SiO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Al2O3</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>클링커 Al2O3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Fe2O3</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>클링커 Fe2O3</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>CaO</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>클링커 CaO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>MgO</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>클링커 MgO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>SO3</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>클링커 SO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Na2O</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>클링커 Na2O</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>K2O</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>클링커 K2O</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>F-CaO(XRF)</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>클링커 유리석회(f-CaO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>F-CaO(습식)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>클링커 유리석회(f-CaO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>용중</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>클링커 용적비중(용중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>3종시멘트성적(출하)</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>물성 + 출하시멘트</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>품명</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>품명(품종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>압축강도1일(MPa)</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>압축강도 1일</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>압축강도3일(MPa)</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>압축강도 3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>압축강도7일(MPa)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>압축강도 7일</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>압축강도28일(MPa)</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>압축강도 28일</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Autoclave</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Autoclave</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>초결시간(분)</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>초결시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>종결시간(HH:MM)</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>종결시간</t>
         </is>
@@ -2529,7 +3107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C139"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2569,7 +3147,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>SO3(CS분석)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2586,7 +3164,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>90㎛</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2603,7 +3181,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>주도</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2620,7 +3198,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>간이flow</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2637,7 +3215,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SO3(CS분석)</t>
+          <t>초결시간(분)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2654,7 +3232,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>종결시간(HH:MM)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2666,12 +3244,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>시멘트공정(밀 출구)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>첨가재명칭</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2683,12 +3261,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>시멘트공정(밀 출구)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>석회석비율</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2700,12 +3278,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>시멘트공정(밀 출구)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>석회석CO2</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2717,12 +3295,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>시멘트공정(밀 출구)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>90㎛</t>
+          <t>석회석품위</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2734,12 +3312,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>시멘트공정(밀 출구)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>주도</t>
+          <t>첨가재비율</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2751,12 +3329,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>시멘트공정(밀 출구)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>간이flow</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -2768,12 +3346,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>시멘트공정(밀 출구)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>초결시간(분)</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2785,12 +3363,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>시멘트공정(밀 출구)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>종결시간(HH:MM)</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2807,7 +3385,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>첨가재명칭</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2824,7 +3402,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>석회석비율</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2841,7 +3419,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>석회석CO2</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2858,7 +3436,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>석회석품위</t>
+          <t>SO3(XRF)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2875,7 +3453,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>첨가재비율</t>
+          <t>SO3(C/S)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2892,7 +3470,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2909,7 +3487,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2926,7 +3504,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2943,7 +3521,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>Cl(습식)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2960,7 +3538,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2977,7 +3555,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>F-CaO(습식)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2994,7 +3572,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SO3(XRF)</t>
+          <t>P2O5(XRF)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3011,7 +3589,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SO3(C/S)</t>
+          <t>총크롬</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -3028,7 +3606,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>밀도</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3045,7 +3623,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>90㎛</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -3062,7 +3640,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>45㎛</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3079,7 +3657,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Cl(습식)</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -3096,7 +3674,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>주도</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3113,7 +3691,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(습식)</t>
+          <t>Flow</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3130,7 +3708,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>P2O5(XRF)</t>
+          <t>간이Flow</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3147,7 +3725,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>총크롬</t>
+          <t>공기량</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3164,7 +3742,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>밀도</t>
+          <t>콘크리트Flow</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3181,7 +3759,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>90㎛</t>
+          <t>콘크리트단위수량</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3198,7 +3776,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>45㎛</t>
+          <t>콘크리트강도3일(MPa)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3215,7 +3793,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>콘크리트강도7일(MPa)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3232,7 +3810,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>주도</t>
+          <t>콘크리트강도28일(MPa)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3249,7 +3827,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Flow</t>
+          <t>P205(습식)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3266,7 +3844,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>간이Flow</t>
+          <t>F(습식)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3283,7 +3861,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>공기량</t>
+          <t>첨가재명칭</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3300,7 +3878,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>콘크리트Flow</t>
+          <t>석회석비율</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3317,7 +3895,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>콘크리트단위수량</t>
+          <t>석회석CO2</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3334,7 +3912,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도3일(MPa)</t>
+          <t>석회석품위</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3351,7 +3929,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도7일(MPa)</t>
+          <t>첨가재비율</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3368,7 +3946,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도28일(MPa)</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3385,7 +3963,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>P205(습식)</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3402,7 +3980,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>F(습식)</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3419,7 +3997,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>첨가재명칭</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3436,7 +4014,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>석회석비율</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -3453,7 +4031,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>석회석CO2</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3470,7 +4048,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>석회석품위</t>
+          <t>SO3(XRF)</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3487,7 +4065,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>첨가재비율</t>
+          <t>SO3(C/S)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3504,7 +4082,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3521,7 +4099,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3538,7 +4116,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3555,7 +4133,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>Cl(습식)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3572,7 +4150,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3589,7 +4167,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>F-CaO(습식)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -3606,7 +4184,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SO3(XRF)</t>
+          <t>P2O5(XRF)</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3623,7 +4201,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SO3(C/S)</t>
+          <t>총크롬</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -3640,7 +4218,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>밀도</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3657,7 +4235,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>90㎛</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -3674,7 +4252,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>45㎛</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3691,7 +4269,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Cl(습식)</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -3708,7 +4286,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>주도</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3725,7 +4303,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(습식)</t>
+          <t>Flow</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -3742,7 +4320,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>P2O5(XRF)</t>
+          <t>간이Flow</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3759,7 +4337,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>총크롬</t>
+          <t>공기량</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -3776,7 +4354,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>밀도</t>
+          <t>콘크리트Flow</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3793,7 +4371,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>90㎛</t>
+          <t>콘크리트단위수량</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -3810,7 +4388,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>45㎛</t>
+          <t>콘크리트강도3일(MPa)</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3827,7 +4405,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>콘크리트강도7일(MPa)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -3844,7 +4422,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>주도</t>
+          <t>콘크리트강도28일(MPa)</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -3861,7 +4439,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Flow</t>
+          <t>P205(습식)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -3878,7 +4456,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>간이Flow</t>
+          <t>F(습식)</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3890,12 +4468,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>공기량</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -3907,12 +4485,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>콘크리트Flow</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3924,12 +4502,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>콘크리트단위수량</t>
+          <t>F(XRF)</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -3941,12 +4519,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도3일(MPa)</t>
+          <t>온도</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3958,12 +4536,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도7일(MPa)</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -3975,12 +4553,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도28일(MPa)</t>
+          <t>F(XRF)</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3992,12 +4570,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>P205(습식)</t>
+          <t>F(습식)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -4009,12 +4587,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>F(습식)</t>
+          <t>건식F/A(톤)</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -4026,12 +4604,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>Cl</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -4043,12 +4621,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>F(XRF)</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -4060,12 +4638,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>조합원료성적(생료·킬른 피드)</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>F(XRF)</t>
+          <t>F(습식)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -4077,12 +4655,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>온도</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -4094,7 +4672,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4111,7 +4689,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4128,12 +4706,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>F(습식)</t>
+          <t>온도</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -4145,12 +4723,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>석회석(%)</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -4162,12 +4740,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Shale(%)</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -4179,12 +4757,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>실리카(%)</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -4196,12 +4774,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>고품위삼고(%)</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -4213,12 +4791,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>규석(%)</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -4230,12 +4808,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>주물사(%)</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -4247,12 +4825,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>철질(%)</t>
+          <t>SO3(XRF)</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -4264,12 +4842,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Coal Shale(%)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -4281,12 +4859,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>투입량 계(%)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -4298,12 +4876,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>건식F/A(톤)</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -4315,12 +4893,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Cl</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -4332,12 +4910,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>F(XRF)</t>
+          <t>SO3(CS분석)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -4349,12 +4927,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>F(습식)</t>
+          <t>밀도</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -4366,12 +4944,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>석회석(%)</t>
+          <t>90㎛</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -4383,12 +4961,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>경석(%)</t>
+          <t>45㎛</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -4400,12 +4978,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>규석(%)</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -4417,12 +4995,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>석탄회(%)</t>
+          <t>주도</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -4434,457 +5012,15 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>삼고(%)</t>
+          <t>Flow</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>철질(%)</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>주물사(%)</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>실리카(%)</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>투입량 계(%)</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>크링커성적(4·5호)</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>LOI</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>크링커성적(4·5호)</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Cl(XRF)</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>크링커성적(4·5호)</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>F(XRF)</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>크링커성적(4·5호)</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>온도</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>LOI</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>SiO2</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Al2O3</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>Fe2O3</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>CaO</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>MgO</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>SO3(XRF)</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>Na2O</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>K2O</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Cl(XRF)</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>F-CaO(XRF)</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>SO3(CS분석)</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>밀도</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>90㎛</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>45㎛</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>Blaine</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>주도</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>Flow</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
         </is>

--- a/docs/LIMS_공정별_열매칭표.xlsx
+++ b/docs/LIMS_공정별_열매칭표.xlsx
@@ -691,12 +691,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>생료 (raw_meal)</t>
+          <t>원료 (raw_meal)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -716,12 +716,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>생료 (raw_meal)</t>
+          <t>원료 (raw_meal)</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1823,12 +1823,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1860,19 +1860,19 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>생료 LOI</t>
+          <t>원료 LOI</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1882,19 +1882,19 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>생료 SiO2</t>
+          <t>원료 SiO2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1904,19 +1904,19 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>생료 Al2O3</t>
+          <t>원료 Al2O3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1926,19 +1926,19 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>생료 Fe2O3</t>
+          <t>원료 Fe2O3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1948,19 +1948,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>생료 CaO</t>
+          <t>원료 CaO</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1970,19 +1970,19 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>생료 MgO</t>
+          <t>원료 MgO</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -1992,19 +1992,19 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>생료 SO3</t>
+          <t>원료 SO3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2014,19 +2014,19 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>생료 Na2O</t>
+          <t>원료 Na2O</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>생료 K2O</t>
+          <t>원료 K2O</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2087,12 +2087,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2197,12 +2197,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2219,12 +2219,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2278,19 +2278,19 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>생료 LOI</t>
+          <t>원료 LOI</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2300,19 +2300,19 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>생료 SiO2</t>
+          <t>원료 SiO2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2322,19 +2322,19 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>생료 Al2O3</t>
+          <t>원료 Al2O3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>생료 Fe2O3</t>
+          <t>원료 Fe2O3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2366,19 +2366,19 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>생료 CaO</t>
+          <t>원료 CaO</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2388,19 +2388,19 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>생료 MgO</t>
+          <t>원료 MgO</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2410,19 +2410,19 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>생료 SO3</t>
+          <t>원료 SO3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -2432,19 +2432,19 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>생료 Na2O</t>
+          <t>원료 Na2O</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -2454,19 +2454,19 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>생료 K2O</t>
+          <t>원료 K2O</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -2549,12 +2549,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>생료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4553,7 +4553,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4587,7 +4587,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4604,7 +4604,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(생료·킬른 피드)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">

--- a/docs/LIMS_공정별_열매칭표.xlsx
+++ b/docs/LIMS_공정별_열매칭표.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>자동계산 9 · 미저장 36</t>
+          <t>자동계산 9 · 미저장 37</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>자동계산 9 · 미저장 36</t>
+          <t>자동계산 9 · 미저장 37</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>자동계산 9 · 미저장 18</t>
+          <t>자동계산 9 · 미저장 19</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>시멘트밀공정</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>시멘트 LOI</t>
+          <t>공정구분(호기·밀)</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>cem_sio2</t>
+          <t>시멘트 LOI</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>cem_al2o3</t>
+          <t>cem_sio2</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>cem_fe2o3</t>
+          <t>cem_al2o3</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>cem_cao</t>
+          <t>cem_fe2o3</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>시멘트 MgO</t>
+          <t>cem_cao</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SO3(XRF)</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>시멘트 SO3</t>
+          <t>시멘트 MgO</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>SO3(XRF)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>cem_na2o</t>
+          <t>시멘트 SO3</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>cem_k2o</t>
+          <t>cem_na2o</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>cem_cl</t>
+          <t>cem_k2o</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>cem_fcao</t>
+          <t>cem_cl</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>45㎛</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>시멘트 45㎛</t>
+          <t>cem_fcao</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>45㎛</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>시멘트 Blaine</t>
+          <t>시멘트 45㎛</t>
         </is>
       </c>
     </row>
@@ -1151,34 +1151,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>원료온도</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>시멘트 밀온도</t>
+          <t>시멘트 Blaine</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>시멘트공정(밀 출구)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>원료온도</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>시멘트 밀온도</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>압축강도1일(MPa)</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>압축강도 1일</t>
+          <t>품명(품종)</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>압축강도3일(MPa)</t>
+          <t>압축강도1일(MPa)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>압축강도 3일</t>
+          <t>압축강도 1일</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>압축강도7일(MPa)</t>
+          <t>압축강도3일(MPa)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>압축강도 7일</t>
+          <t>압축강도 3일</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>압축강도28일(MPa)</t>
+          <t>압축강도7일(MPa)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>압축강도 28일</t>
+          <t>압축강도 7일</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>압축강도28일(MPa)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>압축강도 28일</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>6가크롬</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>6가크롬</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>초결시간(분)</t>
+          <t>Autoclave</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>초결시간</t>
+          <t>Autoclave</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>종결시간(HH:MM)</t>
+          <t>초결시간(분)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>종결시간</t>
+          <t>초결시간</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>종결시간(HH:MM)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>종결시간</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>압축강도1일(MPa)</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>압축강도 1일</t>
+          <t>품명(품종)</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>압축강도3일(MPa)</t>
+          <t>압축강도1일(MPa)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>압축강도 3일</t>
+          <t>압축강도 1일</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>압축강도7일(MPa)</t>
+          <t>압축강도3일(MPa)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>압축강도 7일</t>
+          <t>압축강도 3일</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>압축강도28일(MPa)</t>
+          <t>압축강도7일(MPa)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>압축강도 28일</t>
+          <t>압축강도 7일</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>압축강도28일(MPa)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>압축강도 28일</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>6가크롬</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>6가크롬</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>초결시간(분)</t>
+          <t>Autoclave</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>초결시간</t>
+          <t>Autoclave</t>
         </is>
       </c>
     </row>
@@ -1547,34 +1547,34 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>종결시간(HH:MM)</t>
+          <t>초결시간(분)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>종결시간</t>
+          <t>초결시간</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>물성 + 출하시멘트</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>종결시간(HH:MM)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>종결시간</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>클링커 SiO2</t>
+          <t>종류(품명 원문)</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>크링커공정</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>클링커 Al2O3</t>
+          <t>공정구분(호기·밀)</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>클링커 Fe2O3</t>
+          <t>클링커 SiO2</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>클링커 CaO</t>
+          <t>클링커 Al2O3</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>클링커 MgO</t>
+          <t>클링커 Fe2O3</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>클링커 SO3</t>
+          <t>클링커 CaO</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>클링커 Na2O</t>
+          <t>클링커 MgO</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>SO3</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>클링커 K2O</t>
+          <t>클링커 SO3</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>클링커 Na2O</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(습식)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>클링커 K2O</t>
         </is>
       </c>
     </row>
@@ -1811,56 +1811,56 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>용중</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>클링커 용적비중(용중)</t>
+          <t>클링커 유리석회(f-CaO)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(원료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>원료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>F-CaO(습식)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>클링커 유리석회(f-CaO)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(원료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>원료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>용중</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>원료 LOI</t>
+          <t>클링커 용적비중(용중)</t>
         </is>
       </c>
     </row>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>원료 SiO2</t>
+          <t>종류(품명 원문)</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>공정구분</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>원료 Al2O3</t>
+          <t>공정구분(호기·밀)</t>
         </is>
       </c>
     </row>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>원료 Fe2O3</t>
+          <t>원료 LOI</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>원료 CaO</t>
+          <t>원료 SiO2</t>
         </is>
       </c>
     </row>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>원료 MgO</t>
+          <t>원료 Al2O3</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>원료 SO3</t>
+          <t>원료 Fe2O3</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>원료 Na2O</t>
+          <t>원료 CaO</t>
         </is>
       </c>
     </row>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>원료 K2O</t>
+          <t>원료 MgO</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>석회석(%)</t>
+          <t>SO3</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_lime</t>
+          <t>원료 SO3</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Shale(%)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_shale</t>
+          <t>원료 Na2O</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>실리카(%)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_silica2</t>
+          <t>원료 K2O</t>
         </is>
       </c>
     </row>
@@ -2119,12 +2119,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>고품위삼고(%)</t>
+          <t>석회석(%)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_sago</t>
+          <t>rm_mx_lime</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>규석(%)</t>
+          <t>Shale(%)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_silica</t>
+          <t>rm_mx_shale</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>주물사(%)</t>
+          <t>실리카(%)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_sand</t>
+          <t>rm_mx_silica2</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>철질(%)</t>
+          <t>고품위삼고(%)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_iron</t>
+          <t>rm_mx_sago</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Coal Shale(%)</t>
+          <t>규석(%)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_ash</t>
+          <t>rm_mx_silica</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2229,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>투입량 계(%)</t>
+          <t>주물사(%)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_total</t>
+          <t>rm_mx_sand</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>철질(%)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>rm_mx_iron</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2273,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>Coal Shale(%)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>원료 LOI</t>
+          <t>rm_mx_ash</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>투입량 계(%)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>원료 SiO2</t>
+          <t>rm_mx_total</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>원료 Al2O3</t>
+          <t>종류(품명 원문)</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>공정구분</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>원료 Fe2O3</t>
+          <t>공정구분(호기·밀)</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2361,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>원료 CaO</t>
+          <t>원료 LOI</t>
         </is>
       </c>
     </row>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>원료 MgO</t>
+          <t>원료 SiO2</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>원료 SO3</t>
+          <t>원료 Al2O3</t>
         </is>
       </c>
     </row>
@@ -2427,12 +2427,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>원료 Na2O</t>
+          <t>원료 Fe2O3</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>원료 K2O</t>
+          <t>원료 CaO</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>석회석(%)</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_lime</t>
+          <t>원료 MgO</t>
         </is>
       </c>
     </row>
@@ -2493,12 +2493,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>경석(%)</t>
+          <t>SO3</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_shale</t>
+          <t>원료 SO3</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2515,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>규석(%)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_silica</t>
+          <t>원료 Na2O</t>
         </is>
       </c>
     </row>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>석탄회(%)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_ash</t>
+          <t>원료 K2O</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>삼고(%)</t>
+          <t>석회석(%)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_sago</t>
+          <t>rm_mx_lime</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>철질(%)</t>
+          <t>경석(%)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_iron</t>
+          <t>rm_mx_shale</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>주물사(%)</t>
+          <t>규석(%)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_sand</t>
+          <t>rm_mx_silica</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>실리카(%)</t>
+          <t>석탄회(%)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_silica2</t>
+          <t>rm_mx_ash</t>
         </is>
       </c>
     </row>
@@ -2647,100 +2647,100 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>투입량 계(%)</t>
+          <t>삼고(%)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_total</t>
+          <t>rm_mx_sago</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>철질(%)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>rm_mx_iron</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>주물사(%)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>클링커 SiO2</t>
+          <t>rm_mx_sand</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>실리카(%)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>클링커 Al2O3</t>
+          <t>rm_mx_silica2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>투입량 계(%)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>클링커 Fe2O3</t>
+          <t>rm_mx_total</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>클링커 CaO</t>
+          <t>종류(품명 원문)</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>클링커공정</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>클링커 MgO</t>
+          <t>공정구분(호기·밀)</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2801,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>클링커 SO3</t>
+          <t>클링커 SiO2</t>
         </is>
       </c>
     </row>
@@ -2823,12 +2823,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>클링커 Na2O</t>
+          <t>클링커 Al2O3</t>
         </is>
       </c>
     </row>
@@ -2845,12 +2845,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>클링커 K2O</t>
+          <t>클링커 Fe2O3</t>
         </is>
       </c>
     </row>
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>클링커 CaO</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(습식)</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>클링커 MgO</t>
         </is>
       </c>
     </row>
@@ -2911,122 +2911,122 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>용중</t>
+          <t>SO3</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>클링커 용적비중(용중)</t>
+          <t>클링커 SO3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>클링커 Na2O</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>압축강도1일(MPa)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>압축강도 1일</t>
+          <t>클링커 K2O</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>압축강도3일(MPa)</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>압축강도 3일</t>
+          <t>클링커 유리석회(f-CaO)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>압축강도7일(MPa)</t>
+          <t>F-CaO(습식)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>압축강도 7일</t>
+          <t>클링커 유리석회(f-CaO)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>압축강도28일(MPa)</t>
+          <t>용중</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>압축강도 28일</t>
+          <t>클링커 용적비중(용중)</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>품명(품종)</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3065,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>초결시간(분)</t>
+          <t>압축강도1일(MPa)</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>초결시간</t>
+          <t>압축강도 1일</t>
         </is>
       </c>
     </row>
@@ -3087,10 +3087,120 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
+          <t>압축강도3일(MPa)</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>압축강도 3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>압축강도7일(MPa)</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>압축강도 7일</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>압축강도28일(MPa)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>압축강도 28일</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Autoclave</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Autoclave</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>초결시간(분)</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>초결시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
           <t>종결시간(HH:MM)</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>종결시간</t>
         </is>
@@ -3107,7 +3217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C113"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3249,7 +3359,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>첨가재명칭</t>
+          <t>공정구분</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -3266,7 +3376,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>석회석비율</t>
+          <t>첨가재명칭</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -3283,7 +3393,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>석회석CO2</t>
+          <t>석회석비율</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -3300,7 +3410,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>석회석품위</t>
+          <t>석회석CO2</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -3317,7 +3427,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>첨가재비율</t>
+          <t>석회석품위</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3334,7 +3444,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>첨가재비율</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -3351,7 +3461,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3368,7 +3478,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3385,7 +3495,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3402,7 +3512,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3419,7 +3529,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3436,7 +3546,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SO3(XRF)</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -3453,7 +3563,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SO3(C/S)</t>
+          <t>SO3(XRF)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -3470,7 +3580,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>SO3(C/S)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -3487,7 +3597,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -3504,7 +3614,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -3521,7 +3631,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Cl(습식)</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -3538,7 +3648,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>Cl(습식)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3555,7 +3665,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(습식)</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -3572,7 +3682,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>P2O5(XRF)</t>
+          <t>F-CaO(습식)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3589,7 +3699,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>총크롬</t>
+          <t>P2O5(XRF)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -3606,7 +3716,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>밀도</t>
+          <t>총크롬</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3623,7 +3733,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>90㎛</t>
+          <t>밀도</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -3640,7 +3750,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>45㎛</t>
+          <t>90㎛</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3657,7 +3767,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>45㎛</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -3674,7 +3784,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>주도</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3691,7 +3801,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Flow</t>
+          <t>주도</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3708,7 +3818,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>간이Flow</t>
+          <t>Flow</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3725,7 +3835,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>공기량</t>
+          <t>간이Flow</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3742,7 +3852,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>콘크리트Flow</t>
+          <t>공기량</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3759,7 +3869,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>콘크리트단위수량</t>
+          <t>콘크리트Flow</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3776,7 +3886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도3일(MPa)</t>
+          <t>콘크리트단위수량</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3793,7 +3903,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도7일(MPa)</t>
+          <t>콘크리트강도3일(MPa)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3810,7 +3920,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도28일(MPa)</t>
+          <t>콘크리트강도7일(MPa)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3827,7 +3937,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>P205(습식)</t>
+          <t>콘크리트강도28일(MPa)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3844,7 +3954,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>F(습식)</t>
+          <t>P205(습식)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3861,7 +3971,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>첨가재명칭</t>
+          <t>F(습식)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3878,7 +3988,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>석회석비율</t>
+          <t>공정구분</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3895,7 +4005,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>석회석CO2</t>
+          <t>첨가재명칭</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3912,7 +4022,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>석회석품위</t>
+          <t>석회석비율</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3929,7 +4039,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>첨가재비율</t>
+          <t>석회석CO2</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3946,7 +4056,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>석회석품위</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3963,7 +4073,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>첨가재비율</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3980,7 +4090,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3997,7 +4107,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -4014,7 +4124,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -4031,7 +4141,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4048,7 +4158,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SO3(XRF)</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4065,7 +4175,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SO3(C/S)</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -4082,7 +4192,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>SO3(XRF)</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -4099,7 +4209,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>SO3(C/S)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4116,7 +4226,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4133,7 +4243,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Cl(습식)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -4150,7 +4260,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -4167,7 +4277,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(습식)</t>
+          <t>Cl(습식)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4184,7 +4294,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>P2O5(XRF)</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -4201,7 +4311,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>총크롬</t>
+          <t>F-CaO(습식)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -4218,7 +4328,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>밀도</t>
+          <t>P2O5(XRF)</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -4235,7 +4345,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>90㎛</t>
+          <t>총크롬</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -4252,7 +4362,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>45㎛</t>
+          <t>밀도</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -4269,7 +4379,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>90㎛</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -4286,7 +4396,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>주도</t>
+          <t>45㎛</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -4303,7 +4413,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Flow</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4320,7 +4430,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>간이Flow</t>
+          <t>주도</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -4337,7 +4447,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>공기량</t>
+          <t>Flow</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -4354,7 +4464,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>콘크리트Flow</t>
+          <t>간이Flow</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -4371,7 +4481,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>콘크리트단위수량</t>
+          <t>공기량</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -4388,7 +4498,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도3일(MPa)</t>
+          <t>콘크리트Flow</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -4405,7 +4515,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도7일(MPa)</t>
+          <t>콘크리트단위수량</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -4422,7 +4532,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>콘크리트강도28일(MPa)</t>
+          <t>콘크리트강도3일(MPa)</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -4439,7 +4549,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>P205(습식)</t>
+          <t>콘크리트강도7일(MPa)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -4456,7 +4566,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>F(습식)</t>
+          <t>콘크리트강도28일(MPa)</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -4468,12 +4578,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>P205(습식)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -4485,12 +4595,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>F(습식)</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -4507,7 +4617,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>F(XRF)</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -4524,7 +4634,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>온도</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -4536,12 +4646,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(원료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>F(XRF)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -4553,12 +4663,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(원료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>F(XRF)</t>
+          <t>온도</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -4575,7 +4685,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>F(습식)</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -4592,7 +4702,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>건식F/A(톤)</t>
+          <t>F(XRF)</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -4609,7 +4719,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Cl</t>
+          <t>F(습식)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -4626,7 +4736,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>F(XRF)</t>
+          <t>건식F/A(톤)</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -4643,7 +4753,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>F(습식)</t>
+          <t>Cl</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -4655,12 +4765,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>F(XRF)</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -4672,12 +4782,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>F(습식)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -4694,7 +4804,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>F(XRF)</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -4711,7 +4821,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>온도</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -4723,12 +4833,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>F(XRF)</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -4740,12 +4850,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>온도</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -4762,7 +4872,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>공정구분</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -4779,7 +4889,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -4796,7 +4906,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -4813,7 +4923,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -4830,7 +4940,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SO3(XRF)</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -4847,7 +4957,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -4864,7 +4974,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -4881,7 +4991,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>SO3(XRF)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -4898,7 +5008,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -4915,7 +5025,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SO3(CS분석)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -4932,7 +5042,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>밀도</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -4949,7 +5059,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>90㎛</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -4966,7 +5076,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>45㎛</t>
+          <t>SO3(CS분석)</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -4983,7 +5093,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>밀도</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -5000,7 +5110,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>주도</t>
+          <t>90㎛</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -5017,10 +5127,61 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
+          <t>45㎛</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Blaine</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>주도</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>Flow</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
         </is>

--- a/docs/LIMS_공정별_열매칭표.xlsx
+++ b/docs/LIMS_공정별_열매칭표.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>자동계산 14 · 미저장 4</t>
+          <t>자동계산 14 · 미저장 1</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>자동계산 7 · 미저장 4</t>
+          <t>자동계산 7 · 미저장 5</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -750,11 +750,11 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>자동계산 14 · 미저장 4</t>
+          <t>자동계산 14 · 미저장 1</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -887,12 +887,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>투입SILO</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>시멘트 LOI</t>
+          <t>투입사일로</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>cem_sio2</t>
+          <t>시멘트 LOI</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>cem_al2o3</t>
+          <t>cem_sio2</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>cem_fe2o3</t>
+          <t>cem_al2o3</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>cem_cao</t>
+          <t>cem_fe2o3</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>시멘트 MgO</t>
+          <t>cem_cao</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SO3(XRF)</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>시멘트 SO3</t>
+          <t>시멘트 MgO</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>SO3(XRF)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>cem_na2o</t>
+          <t>시멘트 SO3</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>cem_k2o</t>
+          <t>cem_na2o</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>cem_cl</t>
+          <t>cem_k2o</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>cem_fcao</t>
+          <t>cem_cl</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45㎛</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>시멘트 45㎛</t>
+          <t>cem_fcao</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>45㎛</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>시멘트 Blaine</t>
+          <t>시멘트 45㎛</t>
         </is>
       </c>
     </row>
@@ -1173,34 +1173,34 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>원료온도</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>시멘트 밀온도</t>
+          <t>시멘트 Blaine</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>시멘트성적(1종·출하)</t>
+          <t>시멘트공정(밀 출구)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>시멘트</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>원료온도</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>시멘트 밀온도</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>압축강도1일(MPa)</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>압축강도 1일</t>
+          <t>품명(품종)</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>압축강도3일(MPa)</t>
+          <t>압축강도1일(MPa)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>압축강도 3일</t>
+          <t>압축강도 1일</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>압축강도7일(MPa)</t>
+          <t>압축강도3일(MPa)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>압축강도 7일</t>
+          <t>압축강도 3일</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>압축강도28일(MPa)</t>
+          <t>압축강도7일(MPa)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>압축강도 28일</t>
+          <t>압축강도 7일</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>압축강도28일(MPa)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>압축강도 28일</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>6가크롬</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>6가크롬</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>초결시간(분)</t>
+          <t>Autoclave</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>초결시간</t>
+          <t>Autoclave</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>종결시간(HH:MM)</t>
+          <t>초결시간(분)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>종결시간</t>
+          <t>초결시간</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>종결시간(HH:MM)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>종결시간</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>압축강도1일(MPa)</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>압축강도 1일</t>
+          <t>품명(품종)</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>압축강도3일(MPa)</t>
+          <t>압축강도1일(MPa)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>압축강도 3일</t>
+          <t>압축강도 1일</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>압축강도7일(MPa)</t>
+          <t>압축강도3일(MPa)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>압축강도 7일</t>
+          <t>압축강도 3일</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>압축강도28일(MPa)</t>
+          <t>압축강도7일(MPa)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>압축강도 28일</t>
+          <t>압축강도 7일</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>압축강도28일(MPa)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>6가크롬</t>
+          <t>압축강도 28일</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>6가크롬</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>6가크롬</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>초결시간(분)</t>
+          <t>Autoclave</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>초결시간</t>
+          <t>Autoclave</t>
         </is>
       </c>
     </row>
@@ -1569,34 +1569,34 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>종결시간(HH:MM)</t>
+          <t>초결시간(분)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>종결시간</t>
+          <t>초결시간</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>시멘트성적(1종·출하)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>물성 + 출하시멘트</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>종결시간(HH:MM)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>종류(품명 원문)</t>
+          <t>종결시간</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>크링커공정</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>공정구분(호기·밀)</t>
+          <t>종류(품명 원문)</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>크링커공정</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>클링커 SiO2</t>
+          <t>공정구분(호기·밀)</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>투입SILO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>클링커 Al2O3</t>
+          <t>투입사일로</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>클링커 Fe2O3</t>
+          <t>클링커 SiO2</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>클링커 CaO</t>
+          <t>클링커 Al2O3</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>클링커 MgO</t>
+          <t>클링커 Fe2O3</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>클링커 SO3</t>
+          <t>클링커 CaO</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>클링커 Na2O</t>
+          <t>클링커 MgO</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>SO3</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>클링커 K2O</t>
+          <t>클링커 SO3</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>클링커 Na2O</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(습식)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>클링커 K2O</t>
         </is>
       </c>
     </row>
@@ -1855,122 +1855,122 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>용중</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>클링커 용적비중(용중)</t>
+          <t>클링커 Cl</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(원료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>원료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>F(XRF)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>종류(품명 원문)</t>
+          <t>클링커 F</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(원료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>원료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>공정구분</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>공정구분(호기·밀)</t>
+          <t>클링커 유리석회(f-CaO)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(원료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>원료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>F-CaO(습식)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>원료 LOI</t>
+          <t>클링커 유리석회(f-CaO)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(원료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>원료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>용중</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>원료 SiO2</t>
+          <t>클링커 용적비중(용중)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(원료·킬른 피드)</t>
+          <t>수출크링커성적(6·7호)</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>원료</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>온도</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>원료 Al2O3</t>
+          <t>클링커 온도</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>원료 Fe2O3</t>
+          <t>종류(품명 원문)</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>공정구분</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>원료 CaO</t>
+          <t>공정구분(호기·밀)</t>
         </is>
       </c>
     </row>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>원료 MgO</t>
+          <t>원료 LOI</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>원료 SO3</t>
+          <t>원료 SiO2</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>원료 Na2O</t>
+          <t>원료 Al2O3</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>원료 K2O</t>
+          <t>원료 Fe2O3</t>
         </is>
       </c>
     </row>
@@ -2119,12 +2119,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>석회석(%)</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_lime</t>
+          <t>원료 CaO</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Shale(%)</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_shale</t>
+          <t>원료 MgO</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>실리카(%)</t>
+          <t>SO3</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_silica2</t>
+          <t>원료 SO3</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>고품위삼고(%)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_sago</t>
+          <t>원료 Na2O</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>규석(%)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_silica</t>
+          <t>원료 K2O</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2229,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>주물사(%)</t>
+          <t>석회석(%)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_sand</t>
+          <t>rm_mx_lime</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>철질(%)</t>
+          <t>Shale(%)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_iron</t>
+          <t>rm_mx_shale</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2273,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Coal Shale(%)</t>
+          <t>실리카(%)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_ash</t>
+          <t>rm_mx_silica2</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>투입량 계(%)</t>
+          <t>고품위삼고(%)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_total</t>
+          <t>rm_mx_sago</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>규석(%)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>종류(품명 원문)</t>
+          <t>rm_mx_silica</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>공정구분</t>
+          <t>주물사(%)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>공정구분(호기·밀)</t>
+          <t>rm_mx_sand</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2361,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>철질(%)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>원료 LOI</t>
+          <t>rm_mx_iron</t>
         </is>
       </c>
     </row>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>Coal Shale(%)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>원료 SiO2</t>
+          <t>rm_mx_ash</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>투입량 계(%)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>원료 Al2O3</t>
+          <t>rm_mx_total</t>
         </is>
       </c>
     </row>
@@ -2427,12 +2427,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>원료 Fe2O3</t>
+          <t>종류(품명 원문)</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>공정구분</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>원료 CaO</t>
+          <t>공정구분(호기·밀)</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>원료 MgO</t>
+          <t>원료 LOI</t>
         </is>
       </c>
     </row>
@@ -2493,12 +2493,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>원료 SO3</t>
+          <t>원료 SiO2</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2515,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>원료 Na2O</t>
+          <t>원료 Al2O3</t>
         </is>
       </c>
     </row>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>원료 K2O</t>
+          <t>원료 Fe2O3</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>석회석(%)</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_lime</t>
+          <t>원료 CaO</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>경석(%)</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_shale</t>
+          <t>원료 MgO</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>규석(%)</t>
+          <t>SO3</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_silica</t>
+          <t>원료 SO3</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>석탄회(%)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_ash</t>
+          <t>원료 Na2O</t>
         </is>
       </c>
     </row>
@@ -2647,12 +2647,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>삼고(%)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_sago</t>
+          <t>원료 K2O</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>철질(%)</t>
+          <t>석회석(%)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_iron</t>
+          <t>rm_mx_lime</t>
         </is>
       </c>
     </row>
@@ -2691,12 +2691,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>주물사(%)</t>
+          <t>경석(%)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_sand</t>
+          <t>rm_mx_shale</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>실리카(%)</t>
+          <t>규석(%)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_silica2</t>
+          <t>rm_mx_silica</t>
         </is>
       </c>
     </row>
@@ -2735,122 +2735,122 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>투입량 계(%)</t>
+          <t>석탄회(%)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>rm_mx_total</t>
+          <t>rm_mx_ash</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>삼고(%)</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>종류(품명 원문)</t>
+          <t>rm_mx_sago</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>클링커공정</t>
+          <t>철질(%)</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>공정구분(호기·밀)</t>
+          <t>rm_mx_iron</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>주물사(%)</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>클링커 SiO2</t>
+          <t>rm_mx_sand</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>실리카(%)</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>클링커 Al2O3</t>
+          <t>rm_mx_silica2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>클링커</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>투입량 계(%)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>클링커 Fe2O3</t>
+          <t>rm_mx_total</t>
         </is>
       </c>
     </row>
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>클링커 CaO</t>
+          <t>종류(품명 원문)</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>클링커공정</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>클링커 MgO</t>
+          <t>공정구분(호기·밀)</t>
         </is>
       </c>
     </row>
@@ -2911,12 +2911,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>SO3</t>
+          <t>투입SILO</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>클링커 SO3</t>
+          <t>투입사일로</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>클링커 Na2O</t>
+          <t>클링커 SiO2</t>
         </is>
       </c>
     </row>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>클링커 K2O</t>
+          <t>클링커 Al2O3</t>
         </is>
       </c>
     </row>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>클링커 Fe2O3</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(습식)</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>클링커 유리석회(f-CaO)</t>
+          <t>클링커 CaO</t>
         </is>
       </c>
     </row>
@@ -3021,186 +3021,384 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>용중</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>클링커 용적비중(용중)</t>
+          <t>클링커 MgO</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>SO3</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>품명(품종)</t>
+          <t>클링커 SO3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>압축강도1일(MPa)</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>압축강도 1일</t>
+          <t>클링커 Na2O</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>압축강도3일(MPa)</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>압축강도 3일</t>
+          <t>클링커 K2O</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>압축강도7일(MPa)</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>압축강도 7일</t>
+          <t>클링커 Cl</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>압축강도28일(MPa)</t>
+          <t>F(XRF)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>압축강도 28일</t>
+          <t>클링커 F</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Autoclave</t>
+          <t>클링커 유리석회(f-CaO)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>3종시멘트성적(출하)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>물성 + 출하시멘트</t>
+          <t>클링커</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>초결시간(분)</t>
+          <t>F-CaO(습식)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>초결시간</t>
+          <t>클링커 유리석회(f-CaO)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>용중</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>클링커 용적비중(용중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>크링커성적(4·5호)</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>클링커</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>온도</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>클링커 온도</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>3종시멘트성적(출하)</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>물성 + 출하시멘트</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>품명</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>품명(품종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>압축강도1일(MPa)</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>압축강도 1일</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>압축강도3일(MPa)</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>압축강도 3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>압축강도7일(MPa)</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>압축강도 7일</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>압축강도28일(MPa)</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>압축강도 28일</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Autoclave</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Autoclave</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>초결시간(분)</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>초결시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>3종시멘트성적(출하)</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>물성 + 출하시멘트</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>종결시간(HH:MM)</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>종결시간</t>
         </is>
@@ -3217,7 +3415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4629,12 +4827,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>투입SILO</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -4646,12 +4844,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>F(XRF)</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -4663,12 +4861,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>수출크링커성적(6·7호)</t>
+          <t>조합원료성적(원료·킬른 피드)</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>온도</t>
+          <t>F(XRF)</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -4685,7 +4883,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>F(습식)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -4702,7 +4900,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>F(XRF)</t>
+          <t>건식F/A(톤)</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -4719,7 +4917,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>F(습식)</t>
+          <t>Cl</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -4736,7 +4934,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>건식F/A(톤)</t>
+          <t>F(XRF)</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -4753,7 +4951,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Cl</t>
+          <t>F(습식)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -4765,12 +4963,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(원료·킬른 피드)</t>
+          <t>크링커성적(4·5호)</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>F(XRF)</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -4782,12 +4980,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>조합원료성적(원료·킬른 피드)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>F(습식)</t>
+          <t>공정구분</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -4799,7 +4997,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4816,12 +5014,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>SiO2</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -4833,12 +5031,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>F(XRF)</t>
+          <t>Al2O3</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -4850,12 +5048,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>크링커성적(4·5호)</t>
+          <t>3종시멘트성적(출하)</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>온도</t>
+          <t>Fe2O3</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -4872,7 +5070,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>공정구분</t>
+          <t>CaO</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -4889,7 +5087,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>MgO</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -4906,7 +5104,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SiO2</t>
+          <t>SO3(XRF)</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -4923,7 +5121,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Al2O3</t>
+          <t>Na2O</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -4940,7 +5138,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Fe2O3</t>
+          <t>K2O</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -4957,7 +5155,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>CaO</t>
+          <t>Cl(XRF)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -4974,7 +5172,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>F-CaO(XRF)</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -4991,7 +5189,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SO3(XRF)</t>
+          <t>SO3(CS분석)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -5008,7 +5206,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Na2O</t>
+          <t>밀도</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -5025,7 +5223,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>K2O</t>
+          <t>90㎛</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -5042,7 +5240,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Cl(XRF)</t>
+          <t>45㎛</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -5059,7 +5257,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>F-CaO(XRF)</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -5076,7 +5274,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SO3(CS분석)</t>
+          <t>주도</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -5093,95 +5291,10 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>밀도</t>
+          <t>Flow</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>90㎛</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>45㎛</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Blaine</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>주도</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>3종시멘트성적(출하)</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Flow</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>현재 QMS 표에 저장 항목 없음(필요 시 추가 가능)</t>
         </is>
